--- a/словари/шемчук.xlsx
+++ b/словари/шемчук.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED935823-EF93-4104-8B63-5EA440EE3A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A84096D-2DE2-44D0-8908-EC657B258C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="4" r:id="rId1"/>
-    <sheet name="составные" sheetId="3" r:id="rId2"/>
-    <sheet name="Неизменные_короткие" sheetId="1" r:id="rId3"/>
-    <sheet name="Неизменные" sheetId="2" r:id="rId4"/>
-    <sheet name="Неизменные_длинные" sheetId="5" r:id="rId5"/>
+    <sheet name="запятые" sheetId="6" r:id="rId2"/>
+    <sheet name="составные" sheetId="3" r:id="rId3"/>
+    <sheet name="Неизменные_короткие" sheetId="1" r:id="rId4"/>
+    <sheet name="Неизменные" sheetId="2" r:id="rId5"/>
+    <sheet name="Неизменные_длинные" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -678,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B678DDF-91A9-48E8-BE0F-0D4541025386}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="61.26953125" customWidth="1"/>
@@ -839,25 +840,17 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" t="s">
         <v>104</v>
       </c>
     </row>
@@ -867,6 +860,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB128F6-6860-4958-AF2E-831CC1F78E3F}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED33B77-A4FE-48AE-9A13-FA7A259937FD}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -984,7 +998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1142,7 +1156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AFEECF-5CA4-4A3D-9836-5735AC26D3E6}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1172,7 +1186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC9C7E18-A466-479A-89BD-4F20E2AD6654}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/словари/шемчук.xlsx
+++ b/словари/шемчук.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A84096D-2DE2-44D0-8908-EC657B258C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6804B58E-9AAE-4F7B-AA51-EA5029DCF22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="4" r:id="rId1"/>
-    <sheet name="запятые" sheetId="6" r:id="rId2"/>
-    <sheet name="составные" sheetId="3" r:id="rId3"/>
-    <sheet name="Неизменные_короткие" sheetId="1" r:id="rId4"/>
-    <sheet name="Неизменные" sheetId="2" r:id="rId5"/>
-    <sheet name="Неизменные_длинные" sheetId="5" r:id="rId6"/>
+    <sheet name="составные_длинные" sheetId="7" r:id="rId2"/>
+    <sheet name="запятые" sheetId="6" r:id="rId3"/>
+    <sheet name="составные" sheetId="3" r:id="rId4"/>
+    <sheet name="Неизменные_короткие" sheetId="1" r:id="rId5"/>
+    <sheet name="Неизменные" sheetId="2" r:id="rId6"/>
+    <sheet name="Неизменные_длинные" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -679,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B678DDF-91A9-48E8-BE0F-0D4541025386}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="61.26953125" customWidth="1"/>
@@ -688,26 +689,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -720,138 +721,155 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" t="s">
-        <v>88</v>
+        <v>85</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B21">
+    <sortCondition ref="A1:A21"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3881F7BD-4813-4E66-8FFF-40E22F6B530D}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="62" customWidth="1"/>
+    <col min="2" max="2" width="26.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB128F6-6860-4958-AF2E-831CC1F78E3F}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -880,7 +898,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED33B77-A4FE-48AE-9A13-FA7A259937FD}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -998,7 +1016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1156,7 +1174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AFEECF-5CA4-4A3D-9836-5735AC26D3E6}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1186,7 +1204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC9C7E18-A466-479A-89BD-4F20E2AD6654}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
